--- a/artfynd/A 34094-2026 artfynd.xlsx
+++ b/artfynd/A 34094-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136054298</v>
       </c>
       <c r="B2" t="n">
-        <v>92348</v>
+        <v>92351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136054329</v>
       </c>
       <c r="B3" t="n">
-        <v>92348</v>
+        <v>92351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136054330</v>
       </c>
       <c r="B4" t="n">
-        <v>92348</v>
+        <v>92351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>136054326</v>
       </c>
       <c r="B25" t="n">
-        <v>92281</v>
+        <v>92284</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>136054333</v>
       </c>
       <c r="B26" t="n">
-        <v>92281</v>
+        <v>92284</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>136054397</v>
       </c>
       <c r="B27" t="n">
-        <v>92281</v>
+        <v>92284</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>136054430</v>
       </c>
       <c r="B28" t="n">
-        <v>91111</v>
+        <v>91113</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>136054398</v>
       </c>
       <c r="B29" t="n">
-        <v>91573</v>
+        <v>91575</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>136054331</v>
       </c>
       <c r="B31" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>136054334</v>
       </c>
       <c r="B32" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>136054392</v>
       </c>
       <c r="B33" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>136054401</v>
       </c>
       <c r="B34" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>136054408</v>
       </c>
       <c r="B35" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>136054279</v>
       </c>
       <c r="B36" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>136054280</v>
       </c>
       <c r="B37" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>136054282</v>
       </c>
       <c r="B38" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>136054284</v>
       </c>
       <c r="B39" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>136054285</v>
       </c>
       <c r="B40" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>136054286</v>
       </c>
       <c r="B41" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>136054288</v>
       </c>
       <c r="B42" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>136054290</v>
       </c>
       <c r="B43" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>136054291</v>
       </c>
       <c r="B44" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>136054293</v>
       </c>
       <c r="B45" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>136054294</v>
       </c>
       <c r="B46" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>136054296</v>
       </c>
       <c r="B47" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>136054297</v>
       </c>
       <c r="B48" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>136054303</v>
       </c>
       <c r="B49" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>136054310</v>
       </c>
       <c r="B50" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>136054311</v>
       </c>
       <c r="B51" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>136054312</v>
       </c>
       <c r="B52" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>136054344</v>
       </c>
       <c r="B53" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>136054345</v>
       </c>
       <c r="B54" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>136054346</v>
       </c>
       <c r="B55" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>136054347</v>
       </c>
       <c r="B56" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>136054348</v>
       </c>
       <c r="B57" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>136054351</v>
       </c>
       <c r="B58" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>136054352</v>
       </c>
       <c r="B59" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
         <v>136054357</v>
       </c>
       <c r="B60" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>136054359</v>
       </c>
       <c r="B61" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         <v>136054360</v>
       </c>
       <c r="B62" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>136054362</v>
       </c>
       <c r="B63" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         <v>136054363</v>
       </c>
       <c r="B64" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>136054367</v>
       </c>
       <c r="B65" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>136054370</v>
       </c>
       <c r="B66" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>136054374</v>
       </c>
       <c r="B67" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>136054377</v>
       </c>
       <c r="B68" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>136054379</v>
       </c>
       <c r="B69" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         <v>136054380</v>
       </c>
       <c r="B70" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>136054381</v>
       </c>
       <c r="B71" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         <v>136054383</v>
       </c>
       <c r="B72" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>136054384</v>
       </c>
       <c r="B73" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>136054385</v>
       </c>
       <c r="B74" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>136054386</v>
       </c>
       <c r="B75" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>136054387</v>
       </c>
       <c r="B76" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>136054391</v>
       </c>
       <c r="B77" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9496,7 +9496,7 @@
         <v>136054393</v>
       </c>
       <c r="B78" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>136054396</v>
       </c>
       <c r="B79" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>136054400</v>
       </c>
       <c r="B80" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>136054402</v>
       </c>
       <c r="B81" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>136054405</v>
       </c>
       <c r="B82" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>136054406</v>
       </c>
       <c r="B83" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>136054407</v>
       </c>
       <c r="B84" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>136054409</v>
       </c>
       <c r="B85" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>136054411</v>
       </c>
       <c r="B86" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>136054415</v>
       </c>
       <c r="B87" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>136054416</v>
       </c>
       <c r="B88" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>136054422</v>
       </c>
       <c r="B89" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>136054426</v>
       </c>
       <c r="B90" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>136054427</v>
       </c>
       <c r="B91" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>136054431</v>
       </c>
       <c r="B92" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>136054433</v>
       </c>
       <c r="B93" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>136054434</v>
       </c>
       <c r="B94" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>136054335</v>
       </c>
       <c r="B95" t="n">
-        <v>92563</v>
+        <v>92566</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>136054413</v>
       </c>
       <c r="B96" t="n">
-        <v>93384</v>
+        <v>93387</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 34094-2026 artfynd.xlsx
+++ b/artfynd/A 34094-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136054298</v>
       </c>
       <c r="B2" t="n">
-        <v>92351</v>
+        <v>92352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136054329</v>
       </c>
       <c r="B3" t="n">
-        <v>92351</v>
+        <v>92352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136054330</v>
       </c>
       <c r="B4" t="n">
-        <v>92351</v>
+        <v>92352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>136054326</v>
       </c>
       <c r="B25" t="n">
-        <v>92284</v>
+        <v>92285</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>136054333</v>
       </c>
       <c r="B26" t="n">
-        <v>92284</v>
+        <v>92285</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>136054397</v>
       </c>
       <c r="B27" t="n">
-        <v>92284</v>
+        <v>92285</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>136054331</v>
       </c>
       <c r="B31" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>136054334</v>
       </c>
       <c r="B32" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>136054392</v>
       </c>
       <c r="B33" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>136054401</v>
       </c>
       <c r="B34" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>136054408</v>
       </c>
       <c r="B35" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>136054279</v>
       </c>
       <c r="B36" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>136054280</v>
       </c>
       <c r="B37" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>136054282</v>
       </c>
       <c r="B38" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>136054284</v>
       </c>
       <c r="B39" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>136054285</v>
       </c>
       <c r="B40" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>136054286</v>
       </c>
       <c r="B41" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>136054288</v>
       </c>
       <c r="B42" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>136054290</v>
       </c>
       <c r="B43" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>136054291</v>
       </c>
       <c r="B44" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>136054293</v>
       </c>
       <c r="B45" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>136054294</v>
       </c>
       <c r="B46" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>136054296</v>
       </c>
       <c r="B47" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>136054297</v>
       </c>
       <c r="B48" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>136054303</v>
       </c>
       <c r="B49" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>136054310</v>
       </c>
       <c r="B50" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>136054311</v>
       </c>
       <c r="B51" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>136054312</v>
       </c>
       <c r="B52" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>136054344</v>
       </c>
       <c r="B53" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>136054345</v>
       </c>
       <c r="B54" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>136054346</v>
       </c>
       <c r="B55" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>136054347</v>
       </c>
       <c r="B56" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>136054348</v>
       </c>
       <c r="B57" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>136054351</v>
       </c>
       <c r="B58" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>136054352</v>
       </c>
       <c r="B59" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
         <v>136054357</v>
       </c>
       <c r="B60" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>136054359</v>
       </c>
       <c r="B61" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         <v>136054360</v>
       </c>
       <c r="B62" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>136054362</v>
       </c>
       <c r="B63" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         <v>136054363</v>
       </c>
       <c r="B64" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>136054367</v>
       </c>
       <c r="B65" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>136054370</v>
       </c>
       <c r="B66" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>136054374</v>
       </c>
       <c r="B67" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>136054377</v>
       </c>
       <c r="B68" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>136054379</v>
       </c>
       <c r="B69" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         <v>136054380</v>
       </c>
       <c r="B70" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>136054381</v>
       </c>
       <c r="B71" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         <v>136054383</v>
       </c>
       <c r="B72" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>136054384</v>
       </c>
       <c r="B73" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>136054385</v>
       </c>
       <c r="B74" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>136054386</v>
       </c>
       <c r="B75" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>136054387</v>
       </c>
       <c r="B76" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>136054391</v>
       </c>
       <c r="B77" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9496,7 +9496,7 @@
         <v>136054393</v>
       </c>
       <c r="B78" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>136054396</v>
       </c>
       <c r="B79" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>136054400</v>
       </c>
       <c r="B80" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>136054402</v>
       </c>
       <c r="B81" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>136054405</v>
       </c>
       <c r="B82" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>136054406</v>
       </c>
       <c r="B83" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>136054407</v>
       </c>
       <c r="B84" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>136054409</v>
       </c>
       <c r="B85" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>136054411</v>
       </c>
       <c r="B86" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>136054415</v>
       </c>
       <c r="B87" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>136054416</v>
       </c>
       <c r="B88" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>136054422</v>
       </c>
       <c r="B89" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>136054426</v>
       </c>
       <c r="B90" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>136054427</v>
       </c>
       <c r="B91" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>136054431</v>
       </c>
       <c r="B92" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>136054433</v>
       </c>
       <c r="B93" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>136054434</v>
       </c>
       <c r="B94" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>136054335</v>
       </c>
       <c r="B95" t="n">
-        <v>92566</v>
+        <v>92567</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>136054413</v>
       </c>
       <c r="B96" t="n">
-        <v>93387</v>
+        <v>93388</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
